--- a/updated_portfolio.xlsx
+++ b/updated_portfolio.xlsx
@@ -522,23 +522,23 @@
         <v>1489.32</v>
       </c>
       <c r="G2" t="n">
-        <v>359.05</v>
+        <v>442.25</v>
       </c>
       <c r="H2" t="n">
-        <v>4308.6</v>
+        <v>5307</v>
       </c>
       <c r="I2" t="n">
-        <v>2819.280000000001</v>
+        <v>3817.68</v>
       </c>
       <c r="J2" t="n">
-        <v>189.2998146805254</v>
+        <v>256.3371202965112</v>
       </c>
       <c r="K2" t="n">
-        <v>2.002840909090912</v>
+        <v>0</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2025-12-01 08:36:44</t>
+          <t>2026-01-04 10:36:39</t>
         </is>
       </c>
     </row>
@@ -566,23 +566,23 @@
         <v>3291.84</v>
       </c>
       <c r="G3" t="n">
-        <v>363.8</v>
+        <v>370.35</v>
       </c>
       <c r="H3" t="n">
-        <v>4365.6</v>
+        <v>4444.200000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>1073.76</v>
+        <v>1152.360000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>32.6188393117527</v>
+        <v>35.00656167979005</v>
       </c>
       <c r="K3" t="n">
-        <v>1.961883408071749</v>
+        <v>0</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2025-12-01 08:36:44</t>
+          <t>2026-01-04 10:36:39</t>
         </is>
       </c>
     </row>
@@ -612,23 +612,23 @@
         <v>9412.82</v>
       </c>
       <c r="G4" t="n">
-        <v>168.63</v>
+        <v>182.8</v>
       </c>
       <c r="H4" t="n">
-        <v>9780.539999999999</v>
+        <v>10602.4</v>
       </c>
       <c r="I4" t="n">
-        <v>367.7199999999993</v>
+        <v>1189.580000000002</v>
       </c>
       <c r="J4" t="n">
-        <v>3.906586973935541</v>
+        <v>12.63787047877259</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3989045010716762</v>
+        <v>-0.04374453193349961</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2025-12-01 08:36:44</t>
+          <t>2026-01-04 10:36:39</t>
         </is>
       </c>
     </row>
@@ -658,23 +658,23 @@
         <v>1489.48</v>
       </c>
       <c r="G5" t="n">
-        <v>1564</v>
+        <v>1642.1</v>
       </c>
       <c r="H5" t="n">
-        <v>1564</v>
+        <v>1642.1</v>
       </c>
       <c r="I5" t="n">
-        <v>74.51999999999998</v>
+        <v>152.6199999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>5.003088326127238</v>
+        <v>10.24652898998307</v>
       </c>
       <c r="K5" t="n">
-        <v>0.249983975386199</v>
+        <v>0.1036332601804327</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2025-12-01 08:36:44</t>
+          <t>2026-01-04 10:36:39</t>
         </is>
       </c>
     </row>
@@ -704,23 +704,23 @@
         <v>42672</v>
       </c>
       <c r="G6" t="n">
-        <v>882.1</v>
+        <v>861</v>
       </c>
       <c r="H6" t="n">
-        <v>42340.8</v>
+        <v>41328</v>
       </c>
       <c r="I6" t="n">
-        <v>-331.1999999999971</v>
+        <v>-1344</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7761529808773835</v>
+        <v>-3.149606299212598</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.380736765610154</v>
+        <v>0.01742463843874975</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2025-12-01 08:36:44</t>
+          <t>2026-01-04 10:36:39</t>
         </is>
       </c>
     </row>
@@ -750,23 +750,23 @@
         <v>3683.25</v>
       </c>
       <c r="G7" t="n">
-        <v>533.3</v>
+        <v>616.55</v>
       </c>
       <c r="H7" t="n">
-        <v>7999.499999999999</v>
+        <v>9248.25</v>
       </c>
       <c r="I7" t="n">
-        <v>4316.249999999999</v>
+        <v>5565</v>
       </c>
       <c r="J7" t="n">
-        <v>117.1859091834657</v>
+        <v>151.089391162696</v>
       </c>
       <c r="K7" t="n">
-        <v>1.387832699619763</v>
+        <v>-0.06483507577600954</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2025-12-01 08:36:44</t>
+          <t>2026-01-04 10:36:39</t>
         </is>
       </c>
     </row>
@@ -796,23 +796,23 @@
         <v>12777.93</v>
       </c>
       <c r="G8" t="n">
-        <v>380.15</v>
+        <v>368.15</v>
       </c>
       <c r="H8" t="n">
-        <v>12544.95</v>
+        <v>12148.95</v>
       </c>
       <c r="I8" t="n">
-        <v>-232.9799999999996</v>
+        <v>-628.9799999999996</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.823300018078043</v>
+        <v>-4.922393533224862</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4274279615795</v>
+        <v>0.1223823769377179</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2025-12-01 08:36:44</t>
+          <t>2026-01-04 10:36:39</t>
         </is>
       </c>
     </row>
@@ -842,23 +842,23 @@
         <v>10452.4</v>
       </c>
       <c r="G9" t="n">
-        <v>389.75</v>
+        <v>392.65</v>
       </c>
       <c r="H9" t="n">
-        <v>15590</v>
+        <v>15706</v>
       </c>
       <c r="I9" t="n">
-        <v>5137.6</v>
+        <v>5253.6</v>
       </c>
       <c r="J9" t="n">
-        <v>49.15234778615438</v>
+        <v>50.26214075236309</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-0.114474688374471</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2025-12-01 08:36:44</t>
+          <t>2026-01-04 10:36:39</t>
         </is>
       </c>
     </row>
@@ -888,23 +888,23 @@
         <v>947.96</v>
       </c>
       <c r="G10" t="n">
-        <v>28.08</v>
+        <v>27.07</v>
       </c>
       <c r="H10" t="n">
-        <v>730.0799999999999</v>
+        <v>703.8200000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-217.8800000000001</v>
+        <v>-244.14</v>
       </c>
       <c r="J10" t="n">
-        <v>-22.98409215578717</v>
+        <v>-25.75425123422929</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5665722379603405</v>
+        <v>0.1479837217905999</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2025-12-01 08:36:44</t>
+          <t>2026-01-04 10:36:39</t>
         </is>
       </c>
     </row>
@@ -934,23 +934,23 @@
         <v>762.4</v>
       </c>
       <c r="G11" t="n">
-        <v>244.83</v>
+        <v>242</v>
       </c>
       <c r="H11" t="n">
-        <v>1224.15</v>
+        <v>1210</v>
       </c>
       <c r="I11" t="n">
-        <v>461.7500000000001</v>
+        <v>447.6</v>
       </c>
       <c r="J11" t="n">
-        <v>60.56532004197274</v>
+        <v>58.7093389296957</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6495375128468704</v>
+        <v>0.2236395262155189</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2025-12-01 08:36:44</t>
+          <t>2026-01-04 10:36:39</t>
         </is>
       </c>
     </row>
@@ -980,23 +980,23 @@
         <v>4550.45</v>
       </c>
       <c r="G12" t="n">
-        <v>795.4</v>
+        <v>755</v>
       </c>
       <c r="H12" t="n">
-        <v>3977</v>
+        <v>3775</v>
       </c>
       <c r="I12" t="n">
-        <v>-573.4499999999998</v>
+        <v>-775.4499999999998</v>
       </c>
       <c r="J12" t="n">
-        <v>-12.60205034666901</v>
+        <v>-17.04117175224428</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6246876561719141</v>
+        <v>-0.033101621979477</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2025-12-01 08:36:44</t>
+          <t>2026-01-04 10:36:39</t>
         </is>
       </c>
     </row>
@@ -1026,23 +1026,23 @@
         <v>4867.200000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>327.1</v>
+        <v>351.65</v>
       </c>
       <c r="H13" t="n">
-        <v>4906.5</v>
+        <v>5274.75</v>
       </c>
       <c r="I13" t="n">
-        <v>39.29999999999927</v>
+        <v>407.5499999999993</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8074457593688211</v>
+        <v>8.37339743589742</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1991116556900089</v>
+        <v>-0.1278046009656477</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2025-12-01 08:36:44</t>
+          <t>2026-01-04 10:36:39</t>
         </is>
       </c>
     </row>
@@ -1072,23 +1072,23 @@
         <v>3716.9</v>
       </c>
       <c r="G14" t="n">
-        <v>684.3</v>
+        <v>694.8</v>
       </c>
       <c r="H14" t="n">
-        <v>3421.5</v>
+        <v>3474</v>
       </c>
       <c r="I14" t="n">
-        <v>-295.4000000000001</v>
+        <v>-242.9000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>-7.947483117651808</v>
+        <v>-6.535015738922223</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.3494975972040325</v>
+        <v>-0.007195797654179781</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2025-12-01 08:36:44</t>
+          <t>2026-01-04 10:36:39</t>
         </is>
       </c>
     </row>
@@ -1118,23 +1118,23 @@
         <v>13152.8</v>
       </c>
       <c r="G15" t="n">
-        <v>146.7</v>
+        <v>134.49</v>
       </c>
       <c r="H15" t="n">
-        <v>11736</v>
+        <v>10759.2</v>
       </c>
       <c r="I15" t="n">
-        <v>-1416.799999999999</v>
+        <v>-2393.599999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>-10.77185086065324</v>
+        <v>-18.19840642296696</v>
       </c>
       <c r="K15" t="n">
-        <v>5.319836312728837</v>
+        <v>0.09675498660315231</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2025-12-01 08:36:44</t>
+          <t>2026-01-04 10:36:39</t>
         </is>
       </c>
     </row>
@@ -1164,23 +1164,23 @@
         <v>3096.78</v>
       </c>
       <c r="G16" t="n">
-        <v>1642.9</v>
+        <v>1640</v>
       </c>
       <c r="H16" t="n">
-        <v>4928.700000000001</v>
+        <v>4920</v>
       </c>
       <c r="I16" t="n">
-        <v>1831.920000000001</v>
+        <v>1823.22</v>
       </c>
       <c r="J16" t="n">
-        <v>59.15563908317676</v>
+        <v>58.87470210993355</v>
       </c>
       <c r="K16" t="n">
-        <v>1.151336042359318</v>
+        <v>-0.01219363492257319</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2025-12-01 08:36:44</t>
+          <t>2026-01-04 10:36:39</t>
         </is>
       </c>
     </row>
@@ -1228,20 +1228,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>116363.53</v>
       </c>
       <c r="C2" t="n">
-        <v>129417.92</v>
+        <v>130543.67</v>
       </c>
       <c r="D2" t="n">
-        <v>13054.38999999998</v>
+        <v>14180.14</v>
       </c>
       <c r="E2" t="n">
-        <v>11.21862666077592</v>
+        <v>12.18606895132865</v>
       </c>
     </row>
   </sheetData>
@@ -1288,20 +1288,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>116363.53</v>
       </c>
       <c r="C2" t="n">
-        <v>129417.92</v>
+        <v>130543.67</v>
       </c>
       <c r="D2" t="n">
-        <v>13054.38999999998</v>
+        <v>14180.14</v>
       </c>
       <c r="E2" t="n">
-        <v>11.21862666077592</v>
+        <v>12.18606895132865</v>
       </c>
     </row>
   </sheetData>

--- a/updated_portfolio.xlsx
+++ b/updated_portfolio.xlsx
@@ -522,23 +522,23 @@
         <v>1489.32</v>
       </c>
       <c r="G2" t="n">
-        <v>442.25</v>
+        <v>382.95</v>
       </c>
       <c r="H2" t="n">
-        <v>5307</v>
+        <v>4595.4</v>
       </c>
       <c r="I2" t="n">
-        <v>3817.68</v>
+        <v>3106.08</v>
       </c>
       <c r="J2" t="n">
-        <v>256.3371202965112</v>
+        <v>208.5569253081943</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>0.8028428533824721</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-01-04 10:36:39</t>
+          <t>2026-05-22 10:20:11</t>
         </is>
       </c>
     </row>
@@ -566,23 +566,23 @@
         <v>3291.84</v>
       </c>
       <c r="G3" t="n">
-        <v>370.35</v>
+        <v>363.35</v>
       </c>
       <c r="H3" t="n">
-        <v>4444.200000000001</v>
+        <v>4360.200000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>1152.360000000001</v>
+        <v>1068.360000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>35.00656167979005</v>
+        <v>32.45479731700206</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.5534800055348</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-01-04 10:36:39</t>
+          <t>2026-05-22 10:20:11</t>
         </is>
       </c>
     </row>
@@ -612,23 +612,23 @@
         <v>9412.82</v>
       </c>
       <c r="G4" t="n">
-        <v>182.8</v>
+        <v>209.19</v>
       </c>
       <c r="H4" t="n">
-        <v>10602.4</v>
+        <v>12133.02</v>
       </c>
       <c r="I4" t="n">
-        <v>1189.580000000002</v>
+        <v>2720.200000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>12.63787047877259</v>
+        <v>28.89888471255161</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.04374453193349961</v>
+        <v>0.2924537347780157</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-01-04 10:36:39</t>
+          <t>2026-05-22 10:20:11</t>
         </is>
       </c>
     </row>
@@ -658,23 +658,23 @@
         <v>1489.48</v>
       </c>
       <c r="G5" t="n">
-        <v>1642.1</v>
+        <v>1174.5</v>
       </c>
       <c r="H5" t="n">
-        <v>1642.1</v>
+        <v>1174.5</v>
       </c>
       <c r="I5" t="n">
-        <v>152.6199999999999</v>
+        <v>-314.98</v>
       </c>
       <c r="J5" t="n">
-        <v>10.24652898998307</v>
+        <v>-21.14697746864678</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1036332601804327</v>
+        <v>-0.56721977649848</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-01-04 10:36:39</t>
+          <t>2026-05-22 10:20:11</t>
         </is>
       </c>
     </row>
@@ -704,23 +704,23 @@
         <v>42672</v>
       </c>
       <c r="G6" t="n">
-        <v>861</v>
+        <v>812.95</v>
       </c>
       <c r="H6" t="n">
-        <v>41328</v>
+        <v>39021.60000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-1344</v>
+        <v>-3650.399999999994</v>
       </c>
       <c r="J6" t="n">
-        <v>-3.149606299212598</v>
+        <v>-8.554555680539918</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01742463843874975</v>
+        <v>1.593351662084479</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-01-04 10:36:39</t>
+          <t>2026-05-22 10:20:11</t>
         </is>
       </c>
     </row>
@@ -750,23 +750,23 @@
         <v>3683.25</v>
       </c>
       <c r="G7" t="n">
-        <v>616.55</v>
+        <v>329.95</v>
       </c>
       <c r="H7" t="n">
-        <v>9248.25</v>
+        <v>4949.25</v>
       </c>
       <c r="I7" t="n">
-        <v>5565</v>
+        <v>1266</v>
       </c>
       <c r="J7" t="n">
-        <v>151.089391162696</v>
+        <v>34.37181836693138</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.06483507577600954</v>
+        <v>0.06065200909779792</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-01-04 10:36:39</t>
+          <t>2026-05-22 10:20:11</t>
         </is>
       </c>
     </row>
@@ -796,23 +796,23 @@
         <v>12777.93</v>
       </c>
       <c r="G8" t="n">
-        <v>368.15</v>
+        <v>339.75</v>
       </c>
       <c r="H8" t="n">
-        <v>12148.95</v>
+        <v>11211.75</v>
       </c>
       <c r="I8" t="n">
-        <v>-628.9799999999996</v>
+        <v>-1566.179999999998</v>
       </c>
       <c r="J8" t="n">
-        <v>-4.922393533224862</v>
+        <v>-12.25691485240566</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1223823769377179</v>
+        <v>-0.3080985915492991</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-01-04 10:36:39</t>
+          <t>2026-05-22 10:20:11</t>
         </is>
       </c>
     </row>
@@ -842,23 +842,23 @@
         <v>10452.4</v>
       </c>
       <c r="G9" t="n">
-        <v>392.65</v>
+        <v>408.9</v>
       </c>
       <c r="H9" t="n">
-        <v>15706</v>
+        <v>16356</v>
       </c>
       <c r="I9" t="n">
-        <v>5253.6</v>
+        <v>5903.6</v>
       </c>
       <c r="J9" t="n">
-        <v>50.26214075236309</v>
+        <v>56.48080823542919</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.114474688374471</v>
+        <v>-0.3897685749086535</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-01-04 10:36:39</t>
+          <t>2026-05-22 10:20:11</t>
         </is>
       </c>
     </row>
@@ -888,23 +888,23 @@
         <v>947.96</v>
       </c>
       <c r="G10" t="n">
-        <v>27.07</v>
+        <v>24.4</v>
       </c>
       <c r="H10" t="n">
-        <v>703.8200000000001</v>
+        <v>634.4</v>
       </c>
       <c r="I10" t="n">
-        <v>-244.14</v>
+        <v>-313.5600000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>-25.75425123422929</v>
+        <v>-33.07734503565552</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1479837217905999</v>
+        <v>-0.8533116619260497</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-01-04 10:36:39</t>
+          <t>2026-05-22 10:20:11</t>
         </is>
       </c>
     </row>
@@ -934,23 +934,23 @@
         <v>762.4</v>
       </c>
       <c r="G11" t="n">
-        <v>242</v>
+        <v>290</v>
       </c>
       <c r="H11" t="n">
-        <v>1210</v>
+        <v>1450</v>
       </c>
       <c r="I11" t="n">
-        <v>447.6</v>
+        <v>687.6</v>
       </c>
       <c r="J11" t="n">
-        <v>58.7093389296957</v>
+        <v>90.18887722980064</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2236395262155189</v>
+        <v>-1.977353388541498</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-01-04 10:36:39</t>
+          <t>2026-05-22 10:20:11</t>
         </is>
       </c>
     </row>
@@ -980,23 +980,23 @@
         <v>4550.45</v>
       </c>
       <c r="G12" t="n">
-        <v>755</v>
+        <v>750.2</v>
       </c>
       <c r="H12" t="n">
-        <v>3775</v>
+        <v>3751</v>
       </c>
       <c r="I12" t="n">
-        <v>-775.4499999999998</v>
+        <v>-799.4499999999998</v>
       </c>
       <c r="J12" t="n">
-        <v>-17.04117175224428</v>
+        <v>-17.56859211726312</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.033101621979477</v>
+        <v>-0.648920672758572</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-01-04 10:36:39</t>
+          <t>2026-05-22 10:20:11</t>
         </is>
       </c>
     </row>
@@ -1026,23 +1026,23 @@
         <v>4867.200000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>351.65</v>
+        <v>388.65</v>
       </c>
       <c r="H13" t="n">
-        <v>5274.75</v>
+        <v>5829.75</v>
       </c>
       <c r="I13" t="n">
-        <v>407.5499999999993</v>
+        <v>962.5499999999993</v>
       </c>
       <c r="J13" t="n">
-        <v>8.37339743589742</v>
+        <v>19.77625739644969</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.1278046009656477</v>
+        <v>0</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-01-04 10:36:39</t>
+          <t>2026-05-22 10:20:11</t>
         </is>
       </c>
     </row>
@@ -1072,23 +1072,23 @@
         <v>3716.9</v>
       </c>
       <c r="G14" t="n">
-        <v>694.8</v>
+        <v>530.25</v>
       </c>
       <c r="H14" t="n">
-        <v>3474</v>
+        <v>2651.25</v>
       </c>
       <c r="I14" t="n">
-        <v>-242.9000000000001</v>
+        <v>-1065.65</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.535015738922223</v>
+        <v>-28.67039737415589</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.007195797654179781</v>
+        <v>0.5880679123589154</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-01-04 10:36:39</t>
+          <t>2026-05-22 10:20:11</t>
         </is>
       </c>
     </row>
@@ -1118,23 +1118,23 @@
         <v>13152.8</v>
       </c>
       <c r="G15" t="n">
-        <v>134.49</v>
+        <v>127.07</v>
       </c>
       <c r="H15" t="n">
-        <v>10759.2</v>
+        <v>10165.6</v>
       </c>
       <c r="I15" t="n">
-        <v>-2393.599999999999</v>
+        <v>-2987.200000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>-18.19840642296696</v>
+        <v>-22.71151389818138</v>
       </c>
       <c r="K15" t="n">
-        <v>0.09675498660315231</v>
+        <v>0.01574183392364897</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-01-04 10:36:39</t>
+          <t>2026-05-22 10:20:11</t>
         </is>
       </c>
     </row>
@@ -1164,23 +1164,23 @@
         <v>3096.78</v>
       </c>
       <c r="G16" t="n">
-        <v>1640</v>
+        <v>1164</v>
       </c>
       <c r="H16" t="n">
-        <v>4920</v>
+        <v>3492</v>
       </c>
       <c r="I16" t="n">
-        <v>1823.22</v>
+        <v>395.2200000000003</v>
       </c>
       <c r="J16" t="n">
-        <v>58.87470210993355</v>
+        <v>12.76228857070894</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.01219363492257319</v>
+        <v>-0.3595274781715498</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-01-04 10:36:39</t>
+          <t>2026-05-22 10:20:11</t>
         </is>
       </c>
     </row>
@@ -1228,20 +1228,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>116363.53</v>
       </c>
       <c r="C2" t="n">
-        <v>130543.67</v>
+        <v>121775.72</v>
       </c>
       <c r="D2" t="n">
-        <v>14180.14</v>
+        <v>5412.190000000002</v>
       </c>
       <c r="E2" t="n">
-        <v>12.18606895132865</v>
+        <v>4.651105032650696</v>
       </c>
     </row>
   </sheetData>
@@ -1288,20 +1288,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>116363.53</v>
       </c>
       <c r="C2" t="n">
-        <v>130543.67</v>
+        <v>121775.72</v>
       </c>
       <c r="D2" t="n">
-        <v>14180.14</v>
+        <v>5412.190000000002</v>
       </c>
       <c r="E2" t="n">
-        <v>12.18606895132865</v>
+        <v>4.651105032650696</v>
       </c>
     </row>
   </sheetData>
